--- a/data/students_template.xlsx
+++ b/data/students_template.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,11 @@
           <t>medicalPin</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>className</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +523,11 @@
           <t>1234</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,6 +575,11 @@
           <t>2222</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,6 +627,11 @@
           <t>3333</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -659,6 +679,11 @@
           <t>4444</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -706,6 +731,11 @@
           <t>5555</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -753,6 +783,11 @@
           <t>6666</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -800,6 +835,11 @@
           <t>7777</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -847,6 +887,11 @@
           <t>8888</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -894,6 +939,11 @@
           <t>9999</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -941,6 +991,11 @@
           <t>2468</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -988,6 +1043,11 @@
           <t>1357</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1035,6 +1095,11 @@
           <t>1212</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1082,6 +1147,11 @@
           <t>2323</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1129,6 +1199,11 @@
           <t>3434</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1176,6 +1251,11 @@
           <t>4545</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1223,6 +1303,11 @@
           <t>5656</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1270,6 +1355,11 @@
           <t>6767</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1317,6 +1407,11 @@
           <t>7878</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1364,6 +1459,11 @@
           <t>8989</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1409,6 +1509,11 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>9090</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
